--- a/website/examples/example_odk_bluetooth_device_inspector.xlsx
+++ b/website/examples/example_odk_bluetooth_device_inspector.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R3d6b55cf94074c21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R8c15f6e8ca304e98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R72d5c5f7c17c4748"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Rebf194f3b6e64174"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rb6b56692d5e943bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R175159ad0aa549f7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -404,7 +404,7 @@
         <x:v>field-list</x:v>
       </x:c>
       <x:c r="E2" s="11" t="str">
-        <x:v>com.example.researchos.EXECUTE_METHOD(method_id='bluetooth_device_inspector')</x:v>
+        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='bluetooth_device_inspector')</x:v>
       </x:c>
       <x:c r="F2" s="11"/>
       <x:c r="G2" s="11"/>
@@ -416,10 +416,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>researchos_execution_id</x:v>
+        <x:v>methodmesh_execution_id</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>ResearchOS execution ID</x:v>
+        <x:v>MethodMesh execution ID</x:v>
       </x:c>
       <x:c r="D3" s="11"/>
       <x:c r="E3" s="11"/>
@@ -433,10 +433,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>researchos_status</x:v>
+        <x:v>methodmesh_status</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>ResearchOS status</x:v>
+        <x:v>MethodMesh status</x:v>
       </x:c>
       <x:c r="D4" s="11"/>
       <x:c r="E4" s="11"/>
@@ -608,7 +608,7 @@
         <x:v>2026072707</x:v>
       </x:c>
       <x:c r="D2" s="12" t="str">
-        <x:v>${researchos_status}</x:v>
+        <x:v>${methodmesh_status}</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
